--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_111_R12.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_111_R12.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8684</v>
+        <v>0.7313</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9346</v>
+        <v>0.3016</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9338</v>
+        <v>0.4297</v>
       </c>
       <c r="G2" t="n">
         <v>-0.9111</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2075</v>
+        <v>1.0704</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6201</v>
+        <v>0.9871</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5874</v>
+        <v>0.0833</v>
       </c>
       <c r="V2" t="n">
         <v>-0.8197</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2773</v>
+        <v>0.704</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1329</v>
+        <v>-0.8406</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4102</v>
+        <v>1.5447</v>
       </c>
       <c r="G3" t="n">
         <v>-1.0911</v>
@@ -688,13 +688,13 @@
         <v>1.1598</v>
       </c>
       <c r="S3" t="n">
-        <v>0.42</v>
+        <v>-0.1533</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9831</v>
+        <v>0.2754</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5632</v>
+        <v>-0.4288</v>
       </c>
       <c r="V3" t="n">
         <v>0.7886</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7432</v>
+        <v>0.305</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2714</v>
+        <v>0.7996</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5282</v>
+        <v>-0.4946</v>
       </c>
       <c r="G4" t="n">
         <v>1.0734</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9739</v>
+        <v>0.5357</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0499</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.076</v>
+        <v>-0.0424</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0722</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. NDIAYE</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7592</v>
+        <v>-0.6278</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9669</v>
+        <v>-0.7601</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2076</v>
+        <v>0.1324</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2367</v>
+        <v>1.4775</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0888</v>
+        <v>-0.4766</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.3255</v>
+        <v>1.9541</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.7655</v>
+        <v>2.2679</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3431</v>
+        <v>0.5749</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.1086</v>
+        <v>1.693</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5288</v>
+        <v>-0.7904</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2543</v>
+        <v>-1.0514</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7831</v>
+        <v>0.261</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6237</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>-4.639</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2429</v>
+        <v>0.0698</v>
       </c>
       <c r="T5" t="n">
-        <v>3.1181</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1248</v>
+        <v>-0.4689</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>G. WATSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3339</v>
+        <v>-1.5528</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.4207</v>
+        <v>-2.0466</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0867</v>
+        <v>0.4938</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.617</v>
+        <v>-2.474</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3193</v>
+        <v>-1.0888</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2977</v>
+        <v>-1.3851</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4201</v>
+        <v>-2.5169</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2927</v>
+        <v>-0.981</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7127</v>
+        <v>-1.5359</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1969</v>
+        <v>0.0429</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.612</v>
+        <v>-0.1078</v>
       </c>
       <c r="O6" t="n">
-        <v>0.415</v>
+        <v>0.1507</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0876</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3706</v>
+        <v>0.867</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4787</v>
+        <v>0.5036</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1081</v>
+        <v>0.3633</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6557</v>
+        <v>-1.9909</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8217</v>
+        <v>-3.0104</v>
       </c>
       <c r="F7" t="n">
-        <v>0.166</v>
+        <v>1.0195</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4775</v>
+        <v>-0.617</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4766</v>
+        <v>-0.3193</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9541</v>
+        <v>-0.2977</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2679</v>
+        <v>-0.4201</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5749</v>
+        <v>0.2927</v>
       </c>
       <c r="L7" t="n">
-        <v>1.693</v>
+        <v>-0.7127</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7904</v>
+        <v>-0.1969</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0514</v>
+        <v>-0.612</v>
       </c>
       <c r="O7" t="n">
-        <v>0.261</v>
+        <v>0.415</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.2473</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.639</v>
+        <v>-3.4793</v>
       </c>
       <c r="R7" t="n">
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9581</v>
+        <v>0.7136</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5228</v>
+        <v>0.8889</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4353</v>
+        <v>-0.1753</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. WATSON</t>
+          <t>M. NDIAYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2281</v>
+        <v>-2.1582</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.6546</v>
+        <v>-3.5002</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4266</v>
+        <v>1.342</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.474</v>
+        <v>-2.2367</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0888</v>
+        <v>0.0888</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3851</v>
+        <v>-2.3255</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.5169</v>
+        <v>-2.7655</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.981</v>
+        <v>0.3431</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5359</v>
+        <v>-3.1086</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0429</v>
+        <v>0.5288</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1078</v>
+        <v>-0.2543</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1507</v>
+        <v>0.7831</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1598</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q8" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8083</v>
+        <v>1.844</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1044</v>
+        <v>1.5848</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2961</v>
+        <v>0.2592</v>
       </c>
       <c r="V8" t="n">
-        <v>1.214</v>
+        <v>-0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6154</v>
+        <v>-3.2451</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7603</v>
+        <v>-3.5244</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1448</v>
+        <v>0.2793</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0067</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1448</v>
+        <v>-0.7745</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3655</v>
+        <v>-0.1296</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7793</v>
+        <v>-0.6449</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.0054</v>
+        <v>-3.7195</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4764</v>
+        <v>-2.3585</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.529</v>
+        <v>-1.361</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1897</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8158</v>
+        <v>-0.5298</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5171</v>
+        <v>-0.349</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2351</v>
+        <v>-4.5986</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9037</v>
+        <v>-5.3008</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6686</v>
+        <v>0.7022</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7427</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9843</v>
+        <v>1.6208</v>
       </c>
       <c r="T11" t="n">
-        <v>1.8442</v>
+        <v>1.447</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1401</v>
+        <v>0.1737</v>
       </c>
       <c r="V11" t="n">
         <v>0.3943</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6252</v>
+        <v>-5.3139</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5969</v>
+        <v>-1.0504</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.0282</v>
+        <v>-4.2635</v>
       </c>
       <c r="G12" t="n">
         <v>-7.5638</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0108</v>
+        <v>1.3221</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8338</v>
+        <v>1.3803</v>
       </c>
       <c r="U12" t="n">
-        <v>0.177</v>
+        <v>-0.0582</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.3866</v>
+        <v>-8.116</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.8165</v>
+        <v>-8.680300000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4299</v>
+        <v>0.5643</v>
       </c>
       <c r="G13" t="n">
         <v>-6.2911</v>
@@ -1468,13 +1468,13 @@
         <v>0.6959</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3664</v>
+        <v>0.9043</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6721</v>
+        <v>0.4641</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3058</v>
+        <v>0.4402</v>
       </c>
       <c r="V13" t="n">
         <v>1.214</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-29.9557</v>
+        <v>-29.5825</v>
       </c>
       <c r="E14" t="n">
-        <v>-30.3446</v>
+        <v>-29.9711</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3888000000000003</v>
+        <v>0.3888000000000014</v>
       </c>
       <c r="G14" t="n">
         <v>-23.573</v>
@@ -1522,7 +1522,7 @@
         <v>-21.5682</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.162500000000001</v>
+        <v>-7.1625</v>
       </c>
       <c r="L14" t="n">
         <v>-14.4054</v>
@@ -1546,13 +1546,13 @@
         <v>11.5978</v>
       </c>
       <c r="S14" t="n">
-        <v>7.116600000000001</v>
+        <v>7.4901</v>
       </c>
       <c r="T14" t="n">
-        <v>7.964399999999999</v>
+        <v>8.3377</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8477999999999999</v>
+        <v>-0.8478000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>1.5772</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.0945</v>
+        <v>6.4312</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3602</v>
+        <v>4.5661</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7344</v>
+        <v>1.8652</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4467</v>
+        <v>5.2352</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4515</v>
+        <v>1.8692</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9952</v>
+        <v>3.3661</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9021</v>
+        <v>3.7807</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4166</v>
+        <v>1.462</v>
       </c>
       <c r="L15" t="n">
         <v>2.3187</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5446</v>
+        <v>1.4545</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8681</v>
+        <v>0.4071</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6764</v>
+        <v>1.0474</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3489</v>
+        <v>-1.3555</v>
       </c>
       <c r="T15" t="n">
-        <v>2.1745</v>
+        <v>-0.2869</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1744</v>
+        <v>-1.0686</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
         <v>-1.0722</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0045</v>
+        <v>6.3323</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3302</v>
+        <v>2.9447</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6743</v>
+        <v>3.3875</v>
       </c>
       <c r="G16" t="n">
-        <v>5.2352</v>
+        <v>4.4467</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8692</v>
+        <v>0.4515</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3661</v>
+        <v>3.9952</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7807</v>
+        <v>1.9021</v>
       </c>
       <c r="K16" t="n">
-        <v>1.462</v>
+        <v>-0.4166</v>
       </c>
       <c r="L16" t="n">
         <v>2.3187</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4545</v>
+        <v>2.5446</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4071</v>
+        <v>0.8681</v>
       </c>
       <c r="O16" t="n">
-        <v>1.0474</v>
+        <v>1.6764</v>
       </c>
       <c r="P16" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7822</v>
+        <v>0.5867</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5228</v>
+        <v>0.7591</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2595</v>
+        <v>-0.1724</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0.2836</v>
       </c>
       <c r="X16" t="n">
         <v>-1.0722</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.5852</v>
+        <v>4.6917</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1997</v>
+        <v>2.0817</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3855</v>
+        <v>2.61</v>
       </c>
       <c r="G17" t="n">
         <v>0.6818</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3673</v>
+        <v>0.4738</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2636</v>
+        <v>0.1456</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1037</v>
+        <v>0.3282</v>
       </c>
       <c r="V17" t="n">
         <v>2.1444</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.7976</v>
+        <v>3.9041</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5034</v>
+        <v>1.3855</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2942</v>
+        <v>2.5187</v>
       </c>
       <c r="G18" t="n">
         <v>2.369</v>
@@ -1858,13 +1858,13 @@
         <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8909</v>
+        <v>-0.7844</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2636</v>
+        <v>0.1456</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.1545</v>
+        <v>-0.93</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.5884</v>
+        <v>3.7057</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6278</v>
+        <v>-0.7458</v>
       </c>
       <c r="F19" t="n">
-        <v>4.2162</v>
+        <v>4.4515</v>
       </c>
       <c r="G19" t="n">
         <v>1.2281</v>
@@ -1936,13 +1936,13 @@
         <v>3.2473</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7067</v>
+        <v>-1.5894</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1098</v>
+        <v>-0.2278</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.5968</v>
+        <v>-1.3616</v>
       </c>
       <c r="V19" t="n">
         <v>0.8197</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.2908</v>
+        <v>3.5838</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5219</v>
+        <v>0.9937</v>
       </c>
       <c r="F20" t="n">
-        <v>2.7688</v>
+        <v>2.59</v>
       </c>
       <c r="G20" t="n">
         <v>4.6607</v>
@@ -2014,13 +2014,13 @@
         <v>3.0154</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5296</v>
+        <v>-1.2366</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6721</v>
+        <v>-0.2003</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8575</v>
+        <v>-1.0363</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5361</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.2203</v>
+        <v>3.0453</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.764</v>
+        <v>-1.1742</v>
       </c>
       <c r="F21" t="n">
-        <v>3.9843</v>
+        <v>4.2195</v>
       </c>
       <c r="G21" t="n">
         <v>5.3474</v>
@@ -2092,13 +2092,13 @@
         <v>3.0154</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.5756</v>
+        <v>-1.7506</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8215</v>
+        <v>-0.2317</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.7541</v>
+        <v>-1.5189</v>
       </c>
       <c r="V21" t="n">
         <v>1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2025</v>
+        <v>0.9166</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0605</v>
+        <v>-0.0574</v>
       </c>
       <c r="F22" t="n">
-        <v>1.142</v>
+        <v>0.974</v>
       </c>
       <c r="G22" t="n">
         <v>1.1685</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3756</v>
+        <v>-0.6616</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1142</v>
+        <v>-0.0037</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4898</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-1.214</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.1654</v>
+        <v>0.7443</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1736</v>
+        <v>-0.5275</v>
       </c>
       <c r="F23" t="n">
-        <v>1.339</v>
+        <v>1.2718</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4214</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8909</v>
+        <v>0.4698</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5623</v>
+        <v>0.2084</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3286</v>
+        <v>0.2614</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4434</v>
+        <v>0.4945</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5119</v>
+        <v>-3.9221</v>
       </c>
       <c r="F24" t="n">
-        <v>4.0685</v>
+        <v>4.4166</v>
       </c>
       <c r="G24" t="n">
         <v>-0.0377</v>
@@ -2326,13 +2326,13 @@
         <v>3.0154</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3851</v>
+        <v>-0.4472</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4832</v>
+        <v>0.1065</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9019</v>
+        <v>-0.5537</v>
       </c>
       <c r="V24" t="n">
         <v>0.2836</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.6907</v>
+        <v>-0.1808</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8127</v>
+        <v>-1.9871</v>
       </c>
       <c r="F25" t="n">
-        <v>1.122</v>
+        <v>1.8063</v>
       </c>
       <c r="G25" t="n">
         <v>-0.0276</v>
@@ -2404,13 +2404,13 @@
         <v>2.3195</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7506</v>
+        <v>-0.2407</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8962</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8544</v>
+        <v>-0.1702</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.8591</v>
+        <v>-2.1401</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.4024</v>
+        <v>-2.8742</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5433</v>
+        <v>0.7342</v>
       </c>
       <c r="G26" t="n">
         <v>-1.0776</v>
@@ -2482,13 +2482,13 @@
         <v>1.3917</v>
       </c>
       <c r="S26" t="n">
-        <v>1.2727</v>
+        <v>0.9917</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9752</v>
+        <v>0.5034</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2974</v>
+        <v>0.4883</v>
       </c>
       <c r="V26" t="n">
         <v>-2.2862</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>29.956</v>
+        <v>31.52860000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6834999999999991</v>
+        <v>0.6833999999999989</v>
       </c>
       <c r="F27" t="n">
-        <v>29.2725</v>
+        <v>30.8453</v>
       </c>
       <c r="G27" t="n">
         <v>23.5731</v>
@@ -2560,13 +2560,13 @@
         <v>26.6746</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.1165</v>
+        <v>-5.543999999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>0.8477999999999999</v>
+        <v>0.8477000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-7.964400000000001</v>
+        <v>-6.391600000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-1.5772</v>
